--- a/Canton_Collective_Weekly_Performance_COLOR.xlsx
+++ b/Canton_Collective_Weekly_Performance_COLOR.xlsx
@@ -161,7 +161,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANTON COLLECTIVE — WEEKLY PERFORMANCE  (May 11 – Jun 21, 2026 · GMV = total_sales)</t>
+          <t xml:space="preserve">CANTON COLLECTIVE — WEEKLY PERFORMANCE  (May 11 – Jun 28, 2026 · GMV = total_sales)</t>
         </is>
       </c>
       <c r="B1" s="1"/>
@@ -180,7 +180,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMMARY — all 6 weeks</t>
+          <t xml:space="preserve">SUMMARY — all 7 weeks</t>
         </is>
       </c>
       <c r="B3" s="2"/>
@@ -510,908 +510,930 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <v>19353.59</v>
+      </c>
+      <c r="C11" s="3">
+        <v>184</v>
+      </c>
+      <c r="D11" s="3">
+        <v>101.75</v>
+      </c>
+      <c r="E11" s="3">
+        <v>31496</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.51%</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+39.1%</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.8%</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-12.3%</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BETTER</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Key findings</t>
         </is>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Finding</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>1</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEADLINE (Jun 15–21): MAMC overtakes 1Jinn Studio as #1 vendor for the first time — 39.0% vs 25.7% (MAMC +16.7pp WoW, 1Jinn −9.8pp).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verdict WORSE: GMV $13,916.50, −7.7% WoW, −11.2% vs trailing 4-wk avg.</t>
+          <t xml:space="preserve">HEADLINE (Jun 22–28): Breakout week — GMV $19,353.59, +39.1% WoW and +27.8% vs 4-wk avg (BETTER), best in trailing-8.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversion stays soft: CVR 0.56→0.44→0.42% over 3 weeks — browse→cart leak, not traffic (sessions flat ~26K).</t>
+          <t xml:space="preserve">MAMC pulls away to 44.1% share (+5.1pp) — runaway #1, supplies all top-3 heroes incl. NEW #1 Dreamy Underwater Garden Slip Maxi ($1,528).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AOV slipped off its peak: $108.00 → $106.56 after climbing every week May–early June.</t>
+          <t xml:space="preserve">2th Desire collapses −6.4pp to 6.0% (only Retro Camisole Layer Top holding); Outtheblue recovers 0.8%→3.7% (+2.9pp).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAMC win is broad (12 SKUs): Lavender Floral hero $847, NEW climber Dusty Rose Bandeau $737, Green Fold Over Skirt $607.</t>
+          <t xml:space="preserve">Driver: traffic surge (+21%, ~31.5K sessions) AND conversion recovery (+20%, CVR 0.42→0.51%) — 3-week browse→cart leak eased.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1Jinn Studio ceding share 46% → 26% since mid-May; Outtheblue spiked then faded (6.6% → 0.8%).</t>
+          <t xml:space="preserve">Full-funnel recovery: cart-add 3.57→3.76%, reach-checkout 1.06→1.17%, completion 0.42→0.51%.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email underutilized: 1 send this week (0617 2th Desire) $75 / 1 conv at 61.5% open; 7 campaigns ~$819 attributed total.</t>
+          <t xml:space="preserve">AOV a mild drag: $106.56 → $101.75 as orders jumped +44% (184 orders).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blind spot: Meta CC ad account (SGD) UNSETTLED / not queryable.</t>
+          <t xml:space="preserve">Email underutilized: 1 send this week (0623 Delete-Ex) $133 / 1 conv at 60.2% open; 8 campaigns ~$952 total (≈0.7% of GMV) — pushing a small vendor, not MAMC.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blind spot: Meta CC ad account (SGD) UNSETTLED / not queryable — cannot confirm if the traffic surge was paid-driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
         <v>9</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YoY −37.2% vs Jun 2025 (214 orders @ $97 vs 128 @ $107 now) — June 2025 already scaled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YoY −12.3% vs Jun 2025 (195 orders @ ~$111 vs 184 @ $102 now) — gap narrowed sharply from −37% last week.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">MAY 2026</t>
         </is>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="0"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">KPIs by week</t>
         </is>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Week</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">GMV</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Orders</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">AOV</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">WoW GMV</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">vs 4-wk Avg</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">YoY</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 11–17</t>
-        </is>
-      </c>
-      <c r="B28" s="11">
-        <v>12555.04</v>
-      </c>
-      <c r="C28" s="11">
-        <v>139</v>
-      </c>
-      <c r="D28" s="11">
-        <v>94.58</v>
-      </c>
-      <c r="E28" s="11">
-        <v>20391</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.55%</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-4.9%</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-36.6%</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+221%</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WORSE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 18–24</t>
+          <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
       <c r="B29" s="11">
-        <v>16016.78</v>
+        <v>12555.04</v>
       </c>
       <c r="C29" s="11">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D29" s="11">
-        <v>97.34</v>
+        <v>94.58</v>
       </c>
       <c r="E29" s="11">
-        <v>24221</v>
+        <v>20391</v>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.61%</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+27.6%</t>
+          <t xml:space="preserve">0.55%</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4.9%</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-5.8%</t>
+          <t xml:space="preserve">-36.6%</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">+360%</t>
+          <t xml:space="preserve">+221%</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WORSE (marginal)</t>
+          <t xml:space="preserve">WORSE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">May 18–24</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <v>16016.78</v>
+      </c>
+      <c r="C30" s="11">
+        <v>166</v>
+      </c>
+      <c r="D30" s="11">
+        <v>97.34</v>
+      </c>
+      <c r="E30" s="11">
+        <v>24221</v>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.61%</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.6%</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-5.8%</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+360%</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WORSE (marginal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">May 25–31</t>
         </is>
       </c>
-      <c r="B30" s="11">
+      <c r="B31" s="11">
         <v>13905.39</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C31" s="11">
         <v>140</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D31" s="11">
         <v>99.8</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E31" s="11">
         <v>25212</v>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0.48%</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-13.2%</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-4.9%</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+78%</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FLAT</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0"/>
-    </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Why — decomposition (GMV = Sessions × Conv Rate × AOV)</t>
         </is>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Transition</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">AOV</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Orders</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">GMV</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Primary driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 04 → May 11</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-18.8%</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-4.8%</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+12.3%</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-12.0%</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-4.9%</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Traffic collapse, cushioned by AOV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 11 → May 18</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+18.8%</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+9.6%</t>
+          <t xml:space="preserve">May 04 → May 11</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-18.8%</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4.8%</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2.9%</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+19.4%</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+27.6%</t>
+          <t xml:space="preserve">+12.3%</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-12.0%</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4.9%</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traffic rebound + conversion lift</t>
+          <t xml:space="preserve">Traffic collapse, cushioned by AOV</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">May 11 → May 18</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+18.8%</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+9.6%</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+2.9%</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+19.4%</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.6%</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traffic rebound + conversion lift</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">May 18 → May 25</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+4.1%</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-21.6%</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+2.5%</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-15.7%</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-13.2%</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">CONVERSION collapse (browse→cart)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0"/>
-    </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Funnel + discounts/returns</t>
         </is>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Week</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Cart Adds</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Reached CO</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Completed</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Discounts</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Returns</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 11–17</t>
-        </is>
-      </c>
-      <c r="B40" s="11">
-        <v>20391</v>
-      </c>
-      <c r="C40" s="11">
-        <v>854</v>
-      </c>
-      <c r="D40" s="11">
-        <v>285</v>
-      </c>
-      <c r="E40" s="11">
-        <v>113</v>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.55%</t>
-        </is>
-      </c>
-      <c r="G40" s="11">
-        <v>-2427.49</v>
-      </c>
-      <c r="H40" s="11">
-        <v>-1771.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 18–24</t>
+          <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
       <c r="B41" s="11">
-        <v>24221</v>
+        <v>20391</v>
       </c>
       <c r="C41" s="11">
-        <v>1070</v>
+        <v>854</v>
       </c>
       <c r="D41" s="11">
-        <v>402</v>
+        <v>285</v>
       </c>
       <c r="E41" s="11">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.61%</t>
+          <t xml:space="preserve">0.55%</t>
         </is>
       </c>
       <c r="G41" s="11">
-        <v>-1856.85</v>
+        <v>-2427.49</v>
       </c>
       <c r="H41" s="11">
-        <v>-1658.25</v>
+        <v>-1771.11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">May 18–24</t>
+        </is>
+      </c>
+      <c r="B42" s="11">
+        <v>24221</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1070</v>
+      </c>
+      <c r="D42" s="11">
+        <v>402</v>
+      </c>
+      <c r="E42" s="11">
+        <v>147</v>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.61%</t>
+        </is>
+      </c>
+      <c r="G42" s="11">
+        <v>-1856.85</v>
+      </c>
+      <c r="H42" s="11">
+        <v>-1658.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">May 25–31</t>
         </is>
       </c>
-      <c r="B42" s="11">
+      <c r="B43" s="11">
         <v>25212</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C43" s="11">
         <v>957</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D43" s="11">
         <v>319</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E43" s="11">
         <v>120</v>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0.48%</t>
         </is>
       </c>
-      <c r="G42" s="11">
+      <c r="G43" s="11">
         <v>-2166.15</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H43" s="11">
         <v>-1159.09</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="0"/>
-    </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="0"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Traffic by referrer source</t>
         </is>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Week</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Direct/Unknown $</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ord</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Social $</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ord</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Search $</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ord</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 11–17</t>
-        </is>
-      </c>
-      <c r="B46" s="11">
-        <v>7998.46</v>
-      </c>
-      <c r="C46" s="11">
-        <v>89</v>
-      </c>
-      <c r="D46" s="11">
-        <v>3369.02</v>
-      </c>
-      <c r="E46" s="11">
-        <v>39</v>
-      </c>
-      <c r="F46" s="11">
-        <v>1187.56</v>
-      </c>
-      <c r="G46" s="11">
-        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 18–24</t>
+          <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
       <c r="B47" s="11">
-        <v>10709.87</v>
+        <v>7998.46</v>
       </c>
       <c r="C47" s="11">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D47" s="11">
-        <v>3544.61</v>
+        <v>3369.02</v>
       </c>
       <c r="E47" s="11">
         <v>39</v>
       </c>
       <c r="F47" s="11">
-        <v>1762.3</v>
+        <v>1187.56</v>
       </c>
       <c r="G47" s="11">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 25–31</t>
+          <t xml:space="preserve">May 18–24</t>
         </is>
       </c>
       <c r="B48" s="11">
-        <v>8783.94</v>
+        <v>10709.87</v>
       </c>
       <c r="C48" s="11">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D48" s="11">
-        <v>3043.26</v>
+        <v>3544.61</v>
       </c>
       <c r="E48" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F48" s="11">
-        <v>2078.19</v>
+        <v>1762.3</v>
       </c>
       <c r="G48" s="11">
         <v>23</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0"/>
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">May 25–31</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <v>8783.94</v>
+      </c>
+      <c r="C49" s="11">
+        <v>86</v>
+      </c>
+      <c r="D49" s="11">
+        <v>3043.26</v>
+      </c>
+      <c r="E49" s="11">
+        <v>31</v>
+      </c>
+      <c r="F49" s="11">
+        <v>2078.19</v>
+      </c>
+      <c r="G49" s="11">
+        <v>23</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Vendor GMV share (% of store)</t>
         </is>
       </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Vendor</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 18–24</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 25–31</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1Jinn Studio</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46.3%</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36.6%</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36.0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAMC</t>
+          <t xml:space="preserve">1Jinn Studio</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">46.3%</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.8%</t>
+          <t xml:space="preserve">36.6%</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.7%</t>
+          <t xml:space="preserve">36.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2th Desire</t>
+          <t xml:space="preserve">MAMC</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.1%</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.2%</t>
+          <t xml:space="preserve">9.8%</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.8%</t>
+          <t xml:space="preserve">24.7%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deleteex</t>
+          <t xml:space="preserve">2th Desire</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -1421,1928 +1443,2241 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.3%</t>
+          <t xml:space="preserve">16.2%</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.9%</t>
+          <t xml:space="preserve">10.8%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">First Floor</t>
+          <t xml:space="preserve">Deleteex</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7%</t>
+          <t xml:space="preserve">18.1%</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.0%</t>
+          <t xml:space="preserve">18.3%</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.9%</t>
+          <t xml:space="preserve">13.9%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1Jinn M2M</t>
+          <t xml:space="preserve">First Floor</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.7%</t>
+          <t xml:space="preserve">4.7%</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.7%</t>
+          <t xml:space="preserve">5.0%</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7%</t>
+          <t xml:space="preserve">7.9%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">1Jinn M2M</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.7%</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7%</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">(blank=shipping)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">10.4%</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">10.2%</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">6.1%</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="0"/>
-    </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="0"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Top products — GMV by week</t>
         </is>
       </c>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Product</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 18–24</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">May 25–31</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lavender Floral Chiffon Slip Mini Dress (MAMC)</t>
-        </is>
-      </c>
-      <c r="B62" s="11">
-        <v>0</v>
-      </c>
-      <c r="C62" s="11">
-        <v>512.05</v>
-      </c>
-      <c r="D62" s="11">
-        <v>1201.2</v>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIMBER / hero</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Fold Over Asymmetric Hem Midi Skirt (MAMC)</t>
+          <t xml:space="preserve">Lavender Floral Chiffon Slip Mini Dress (MAMC)</t>
         </is>
       </c>
       <c r="B63" s="11">
         <v>0</v>
       </c>
       <c r="C63" s="11">
-        <v>0</v>
+        <v>512.05</v>
       </c>
       <c r="D63" s="11">
-        <v>391</v>
+        <v>1201.2</v>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLIMBER</t>
+          <t xml:space="preserve">CLIMBER / hero</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retro Camisole Layer Top (2th Desire)</t>
+          <t xml:space="preserve">Green Fold Over Asymmetric Hem Midi Skirt (MAMC)</t>
         </is>
       </c>
       <c r="B64" s="11">
-        <v>803.61</v>
+        <v>0</v>
       </c>
       <c r="C64" s="11">
-        <v>344.34</v>
+        <v>0</v>
       </c>
       <c r="D64" s="11">
-        <v>276.58</v>
+        <v>391</v>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volatile core</t>
+          <t xml:space="preserve">CLIMBER</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2K Beaded Multi Strap Top</t>
+          <t xml:space="preserve">Retro Camisole Layer Top (2th Desire)</t>
         </is>
       </c>
       <c r="B65" s="11">
-        <v>522.69</v>
+        <v>803.61</v>
       </c>
       <c r="C65" s="11">
-        <v>616.46</v>
+        <v>344.34</v>
       </c>
       <c r="D65" s="11">
-        <v>321.2</v>
+        <v>276.58</v>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Volatile core</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midnight Meow Zip Up Cat Ear Hoodie</t>
+          <t xml:space="preserve">Y2K Beaded Multi Strap Top</t>
         </is>
       </c>
       <c r="B66" s="11">
-        <v>422.96</v>
+        <v>522.69</v>
       </c>
       <c r="C66" s="11">
-        <v>569.26</v>
+        <v>616.46</v>
       </c>
       <c r="D66" s="11">
-        <v>580.26</v>
+        <v>321.2</v>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fading</t>
+          <t xml:space="preserve">Core</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metal Flower Pleated Strapless Mini Dress</t>
+          <t xml:space="preserve">Midnight Meow Zip Up Cat Ear Hoodie</t>
         </is>
       </c>
       <c r="B67" s="11">
-        <v>0</v>
+        <v>422.96</v>
       </c>
       <c r="C67" s="11">
-        <v>549.09</v>
+        <v>569.26</v>
       </c>
       <c r="D67" s="11">
-        <v>540.65</v>
+        <v>580.26</v>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peaked</t>
+          <t xml:space="preserve">Fading</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Metal Flower Pleated Strapless Mini Dress</t>
+        </is>
+      </c>
+      <c r="B68" s="11">
+        <v>0</v>
+      </c>
+      <c r="C68" s="11">
+        <v>549.09</v>
+      </c>
+      <c r="D68" s="11">
+        <v>540.65</v>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peaked</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Polka Dot Stripe Henley Tank 3pc Set</t>
         </is>
       </c>
-      <c r="B68" s="11">
+      <c r="B69" s="11">
         <v>761.92</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C69" s="11">
         <v>507.99</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D69" s="11">
         <v>464.84</v>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Declining</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="0"/>
-    </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="0"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Email campaigns (Klaviyo)</t>
         </is>
       </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Send Date</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Campaign</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Theme</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Recipients</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Open Rate</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Attributed Rev</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv</t>
         </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 13</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0513 CC new drop</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New drop</t>
-        </is>
-      </c>
-      <c r="D72" s="11">
-        <v>91</v>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39.6%</t>
-        </is>
-      </c>
-      <c r="F72" s="11">
-        <v>71</v>
-      </c>
-      <c r="G72" s="11">
-        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 20</t>
+          <t xml:space="preserve">May 13</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0520 MAMC</t>
+          <t xml:space="preserve">0513 CC new drop</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAMC</t>
+          <t xml:space="preserve">New drop</t>
         </is>
       </c>
       <c r="D73" s="11">
-        <v>457</v>
+        <v>91</v>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.9%</t>
+          <t xml:space="preserve">39.6%</t>
         </is>
       </c>
       <c r="F73" s="11">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G73" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">May 20</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0520 MAMC</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAMC</t>
+        </is>
+      </c>
+      <c r="D74" s="11">
+        <v>457</v>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32.9%</t>
+        </is>
+      </c>
+      <c r="F74" s="11">
+        <v>0</v>
+      </c>
+      <c r="G74" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">May 27</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0527 MAMC</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">MAMC</t>
         </is>
       </c>
-      <c r="D74" s="11">
+      <c r="D75" s="11">
         <v>774</v>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">34.4%</t>
         </is>
       </c>
-      <c r="F74" s="11">
+      <c r="F75" s="11">
         <v>41</v>
       </c>
-      <c r="G74" s="11">
+      <c r="G75" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="0"/>
-    </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="0"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">JUNE 2026</t>
         </is>
       </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="0"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
     </row>
     <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="A78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">KPIs by week</t>
         </is>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Week</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">GMV</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Orders</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">AOV</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="G79" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">WoW GMV</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">vs 4-wk Avg</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
+      <c r="I80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">YoY</t>
         </is>
       </c>
-      <c r="J79" s="12" t="inlineStr">
+      <c r="J80" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 1–7</t>
-        </is>
-      </c>
-      <c r="B80" s="14">
-        <v>17663.96</v>
-      </c>
-      <c r="C80" s="14">
-        <v>163</v>
-      </c>
-      <c r="D80" s="14">
-        <v>105.71</v>
-      </c>
-      <c r="E80" s="14">
-        <v>26887</v>
-      </c>
-      <c r="F80" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.56%</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+27.0%</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+26.9%</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-4.8%</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BETTER</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jun 8–14</t>
+          <t xml:space="preserve">Jun 1–7</t>
         </is>
       </c>
       <c r="B81" s="14">
-        <v>15074.88</v>
+        <v>17663.96</v>
       </c>
       <c r="C81" s="14">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="D81" s="14">
-        <v>108</v>
+        <v>105.71</v>
       </c>
       <c r="E81" s="14">
-        <v>25874</v>
+        <v>26887</v>
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.44%</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-14.7%</t>
+          <t xml:space="preserve">0.56%</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.0%</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">+0.3%</t>
+          <t xml:space="preserve">+26.9%</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-17.2%</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FLAT</t>
+          <t xml:space="preserve">-4.8%</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BETTER</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jun 8–14</t>
+        </is>
+      </c>
+      <c r="B82" s="14">
+        <v>15074.88</v>
+      </c>
+      <c r="C82" s="14">
+        <v>133</v>
+      </c>
+      <c r="D82" s="14">
+        <v>108</v>
+      </c>
+      <c r="E82" s="14">
+        <v>25874</v>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.44%</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-14.7%</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+0.3%</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-17.2%</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jun 15–21</t>
         </is>
       </c>
-      <c r="B82" s="14">
+      <c r="B83" s="14">
         <v>13916.5</v>
       </c>
-      <c r="C82" s="14">
+      <c r="C83" s="14">
         <v>128</v>
       </c>
-      <c r="D82" s="14">
+      <c r="D83" s="14">
         <v>106.56</v>
       </c>
-      <c r="E82" s="14">
+      <c r="E83" s="14">
         <v>25933</v>
       </c>
-      <c r="F82" s="14" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0.42%</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-7.7%</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-11.2%</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-37.2%</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
+      <c r="J83" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">WORSE</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="0"/>
-    </row>
     <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <v>19353.59</v>
+      </c>
+      <c r="C84" s="14">
+        <v>184</v>
+      </c>
+      <c r="D84" s="14">
+        <v>101.75</v>
+      </c>
+      <c r="E84" s="14">
+        <v>31496</v>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.51%</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+39.1%</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.8%</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-12.3%</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BETTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Why — decomposition (GMV = Sessions × Conv Rate × AOV)</t>
         </is>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Transition</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">AOV</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Orders</t>
         </is>
       </c>
-      <c r="F85" s="12" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">GMV</t>
         </is>
       </c>
-      <c r="G85" s="12" t="inlineStr">
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Primary driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">May 25 → Jun 01</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+6.6%</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+17.2%</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+5.9%</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+16.4%</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+27.0%</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Broad-based: all three positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 01 → Jun 08</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-3.8%</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-21.7%</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+2.2%</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-18.4%</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-14.7%</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONVERSION collapse (browse→cart)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">May 25 → Jun 01</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+6.6%</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+17.2%</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+5.9%</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+16.4%</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+27.0%</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Broad-based: all three positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 01 → Jun 08</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-3.8%</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-21.7%</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+2.2%</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-18.4%</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-14.7%</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONVERSION collapse (browse→cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jun 08 → Jun 15</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+0.2%</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-2.9%</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-1.3%</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-3.8%</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-7.7%</t>
         </is>
       </c>
-      <c r="G88" s="14" t="inlineStr">
+      <c r="G90" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversion stays soft + AOV off peak (traffic flat)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="0"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 15 → Jun 22</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+21.5%</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+19.8%</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4.5%</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+43.8%</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+39.1%</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traffic surge + CONVERSION recovery (browse→cart leak eases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Funnel + discounts/returns</t>
         </is>
       </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Week</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="C91" s="12" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Cart Adds</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Reached CO</t>
         </is>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Completed</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Conv Rate</t>
         </is>
       </c>
-      <c r="G91" s="12" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Discounts</t>
         </is>
       </c>
-      <c r="H91" s="12" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Returns</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="14" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 1–7</t>
         </is>
       </c>
-      <c r="B92" s="14">
+      <c r="B95" s="14">
         <v>26887</v>
       </c>
-      <c r="C92" s="14">
+      <c r="C95" s="14">
         <v>1042</v>
       </c>
-      <c r="D92" s="14">
+      <c r="D95" s="14">
         <v>327</v>
       </c>
-      <c r="E92" s="14">
+      <c r="E95" s="14">
         <v>150</v>
       </c>
-      <c r="F92" s="14" t="inlineStr">
+      <c r="F95" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0.56%</t>
         </is>
       </c>
-      <c r="G92" s="14">
+      <c r="G95" s="14">
         <v>-1822.65</v>
       </c>
-      <c r="H92" s="14">
+      <c r="H95" s="14">
         <v>-1016.1</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 8–14</t>
         </is>
       </c>
-      <c r="B93" s="14">
+      <c r="B96" s="14">
         <v>25874</v>
       </c>
-      <c r="C93" s="14">
+      <c r="C96" s="14">
         <v>869</v>
       </c>
-      <c r="D93" s="14">
+      <c r="D96" s="14">
         <v>289</v>
       </c>
-      <c r="E93" s="14">
+      <c r="E96" s="14">
         <v>113</v>
       </c>
-      <c r="F93" s="14" t="inlineStr">
+      <c r="F96" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0.44%</t>
         </is>
       </c>
-      <c r="G93" s="14">
+      <c r="G96" s="14">
         <v>-2177.46</v>
       </c>
-      <c r="H93" s="14">
+      <c r="H96" s="14">
         <v>-428.99</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="14" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 15–21</t>
         </is>
       </c>
-      <c r="B94" s="14">
+      <c r="B97" s="14">
         <v>25933</v>
       </c>
-      <c r="C94" s="14">
+      <c r="C97" s="14">
         <v>925</v>
       </c>
-      <c r="D94" s="14">
+      <c r="D97" s="14">
         <v>275</v>
       </c>
-      <c r="E94" s="14">
+      <c r="E97" s="14">
         <v>110</v>
       </c>
-      <c r="F94" s="14" t="inlineStr">
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0.42%</t>
         </is>
       </c>
-      <c r="G94" s="14">
+      <c r="G97" s="14">
         <v>-1498.37</v>
       </c>
-      <c r="H94" s="14">
+      <c r="H97" s="14">
         <v>-561.62</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="0"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Traffic by referrer source</t>
-        </is>
-      </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Week</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Direct/Unknown $</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ord</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Social $</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ord</t>
-        </is>
-      </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Search $</t>
-        </is>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ord</t>
-        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="B98" s="14">
+        <v>31496</v>
+      </c>
+      <c r="C98" s="14">
+        <v>1184</v>
+      </c>
+      <c r="D98" s="14">
+        <v>367</v>
+      </c>
+      <c r="E98" s="14">
+        <v>160</v>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.51%</t>
+        </is>
+      </c>
+      <c r="G98" s="14">
+        <v>-2645.97</v>
+      </c>
+      <c r="H98" s="14">
+        <v>-625.34</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traffic by referrer source</t>
+        </is>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct/Unknown $</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ord</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social $</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ord</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search $</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ord</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jun 1–7</t>
         </is>
       </c>
-      <c r="B98" s="14">
+      <c r="B102" s="14">
         <v>11588.8</v>
       </c>
-      <c r="C98" s="14">
+      <c r="C102" s="14">
         <v>104</v>
       </c>
-      <c r="D98" s="14">
+      <c r="D102" s="14">
         <v>3483.83</v>
       </c>
-      <c r="E98" s="14">
+      <c r="E102" s="14">
         <v>33</v>
       </c>
-      <c r="F98" s="14">
+      <c r="F102" s="14">
         <v>2591.33</v>
       </c>
-      <c r="G98" s="14">
+      <c r="G102" s="14">
         <v>26</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 8–14</t>
         </is>
       </c>
-      <c r="B99" s="14">
+      <c r="B103" s="14">
         <v>9522.26</v>
       </c>
-      <c r="C99" s="14">
+      <c r="C103" s="14">
         <v>82</v>
       </c>
-      <c r="D99" s="14">
+      <c r="D103" s="14">
         <v>3767.02</v>
       </c>
-      <c r="E99" s="14">
+      <c r="E103" s="14">
         <v>35</v>
       </c>
-      <c r="F99" s="14">
+      <c r="F103" s="14">
         <v>1785.6</v>
       </c>
-      <c r="G99" s="14">
+      <c r="G103" s="14">
         <v>16</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 15–21</t>
-        </is>
-      </c>
-      <c r="B100" s="14">
-        <v>9299.36</v>
-      </c>
-      <c r="C100" s="14">
-        <v>78</v>
-      </c>
-      <c r="D100" s="14">
-        <v>2901.45</v>
-      </c>
-      <c r="E100" s="14">
-        <v>33</v>
-      </c>
-      <c r="F100" s="14">
-        <v>1715.69</v>
-      </c>
-      <c r="G100" s="14">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="0"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vendor GMV share (% of store)</t>
-        </is>
-      </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vendor</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 1–7</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 8–14</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 15–21</t>
-        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1Jinn Studio</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31.4%</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35.5%</t>
-        </is>
-      </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25.7%</t>
-        </is>
+          <t xml:space="preserve">Jun 15–21</t>
+        </is>
+      </c>
+      <c r="B104" s="14">
+        <v>9299.36</v>
+      </c>
+      <c r="C104" s="14">
+        <v>78</v>
+      </c>
+      <c r="D104" s="14">
+        <v>2901.45</v>
+      </c>
+      <c r="E104" s="14">
+        <v>33</v>
+      </c>
+      <c r="F104" s="14">
+        <v>1715.69</v>
+      </c>
+      <c r="G104" s="14">
+        <v>17</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAMC</t>
-        </is>
-      </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21.5%</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22.3%</t>
-        </is>
-      </c>
-      <c r="D105" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39.0%</t>
-        </is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="B105" s="14">
+        <v>11873.51</v>
+      </c>
+      <c r="C105" s="14">
+        <v>109</v>
+      </c>
+      <c r="D105" s="14">
+        <v>4334.89</v>
+      </c>
+      <c r="E105" s="14">
+        <v>45</v>
+      </c>
+      <c r="F105" s="14">
+        <v>3145.19</v>
+      </c>
+      <c r="G105" s="14">
+        <v>30</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2th Desire</t>
-        </is>
-      </c>
-      <c r="B106" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.6%</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13.2%</t>
-        </is>
-      </c>
-      <c r="D106" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12.4%</t>
-        </is>
-      </c>
+      <c r="A106" s="0"/>
     </row>
     <row r="107">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deleteex</t>
-        </is>
-      </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12.5%</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13.8%</t>
-        </is>
-      </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.4%</t>
-        </is>
-      </c>
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vendor GMV share (% of store)</t>
+        </is>
+      </c>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="13"/>
+      <c r="J107" s="13"/>
     </row>
     <row r="108">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outtheblue</t>
-        </is>
-      </c>
-      <c r="B108" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.4%</t>
-        </is>
-      </c>
-      <c r="C108" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.6%</t>
-        </is>
-      </c>
-      <c r="D108" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.8%</t>
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vendor</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 1–7</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 8–14</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 15–21</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 22–28</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">First Floor</t>
+          <t xml:space="preserve">1Jinn Studio</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6%</t>
+          <t xml:space="preserve">31.4%</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1%</t>
+          <t xml:space="preserve">35.5%</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0%</t>
+          <t xml:space="preserve">25.7%</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.7%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1Jinn M2M</t>
+          <t xml:space="preserve">MAMC</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4%</t>
+          <t xml:space="preserve">21.5%</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.4%</t>
+          <t xml:space="preserve">22.3%</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4%</t>
+          <t xml:space="preserve">39.0%</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44.1%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">(blank=shipping)</t>
+          <t xml:space="preserve">2th Desire</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1%</t>
+          <t xml:space="preserve">20.6%</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9%</t>
+          <t xml:space="preserve">13.2%</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2%</t>
+          <t xml:space="preserve">12.4%</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.0%</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="0"/>
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deleteex</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.5%</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.8%</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.4%</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5%</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top products — GMV by week</t>
-        </is>
-      </c>
-      <c r="B113" s="13"/>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
-      <c r="J113" s="13"/>
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outtheblue</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.4%</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.6%</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.8%</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7%</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 1–7</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 8–14</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun 15–21</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trend</t>
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First Floor</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6%</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1%</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.0%</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavender Floral Chiffon Slip Mini Dress (MAMC)</t>
-        </is>
-      </c>
-      <c r="B115" s="14">
-        <v>1197.35</v>
-      </c>
-      <c r="C115" s="14">
-        <v>771.16</v>
-      </c>
-      <c r="D115" s="14">
-        <v>847.43</v>
+          <t xml:space="preserve">1Jinn M2M</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4%</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.4%</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4%</t>
+        </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLIMBER / hero</t>
+          <t xml:space="preserve">1.0%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dusty Rose Layered Gauze Bandeau Top (MAMC)</t>
-        </is>
-      </c>
-      <c r="B116" s="14">
-        <v>0</v>
-      </c>
-      <c r="C116" s="14">
-        <v>0</v>
-      </c>
-      <c r="D116" s="14">
-        <v>737.11</v>
+          <t xml:space="preserve">(blank=shipping)</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1%</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9%</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2%</t>
+        </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEW CLIMBER</t>
+          <t xml:space="preserve">5.3%</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green Fold Over Asymmetric Hem Midi Skirt (MAMC)</t>
-        </is>
-      </c>
-      <c r="B117" s="14">
-        <v>326.4</v>
-      </c>
-      <c r="C117" s="14">
-        <v>397.63</v>
-      </c>
-      <c r="D117" s="14">
-        <v>607.41</v>
-      </c>
-      <c r="E117" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIMBER</t>
-        </is>
-      </c>
+      <c r="A117" s="0"/>
     </row>
     <row r="118">
-      <c r="A118" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ruffle Trim Gingham Babydoll Mini Dress (MAMC)</t>
-        </is>
-      </c>
-      <c r="B118" s="14">
-        <v>0</v>
-      </c>
-      <c r="C118" s="14">
-        <v>432.67</v>
-      </c>
-      <c r="D118" s="14">
-        <v>159.8</v>
-      </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emerging</t>
-        </is>
-      </c>
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top products — GMV by week</t>
+        </is>
+      </c>
+      <c r="B118" s="13"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="13"/>
     </row>
     <row r="119">
-      <c r="A119" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Retro Camisole Layer Top (2th Desire)</t>
-        </is>
-      </c>
-      <c r="B119" s="14">
-        <v>693.66</v>
-      </c>
-      <c r="C119" s="14">
-        <v>547.9</v>
-      </c>
-      <c r="D119" s="14">
-        <v>397.29</v>
-      </c>
-      <c r="E119" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Volatile core</t>
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 1–7</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 8–14</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 15–21</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2K Beaded Multi Strap Top</t>
+          <t xml:space="preserve">Dreamy Underwater Garden Slip Maxi Dress (MAMC)</t>
         </is>
       </c>
       <c r="B120" s="14">
-        <v>331.17</v>
+        <v>0</v>
       </c>
       <c r="C120" s="14">
-        <v>594.51</v>
+        <v>0</v>
       </c>
       <c r="D120" s="14">
-        <v>460.85</v>
-      </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Core</t>
+        <v>0</v>
+      </c>
+      <c r="E120" s="14">
+        <v>1527.75</v>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW #1 hero</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outtheblue line (vendor total)</t>
+          <t xml:space="preserve">Dusty Rose Layered Gauze Bandeau Top (MAMC)</t>
         </is>
       </c>
       <c r="B121" s="14">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C121" s="14">
-        <v>989.58</v>
+        <v>0</v>
       </c>
       <c r="D121" s="14">
-        <v>109.97</v>
-      </c>
-      <c r="E121" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiked then faded</t>
+        <v>737.11</v>
+      </c>
+      <c r="E121" s="14">
+        <v>1471.06</v>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIMBER → hero</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midnight Meow Zip Up Cat Ear Hoodie</t>
+          <t xml:space="preserve">Lavender Floral Chiffon Slip Mini Dress (MAMC)</t>
         </is>
       </c>
       <c r="B122" s="14">
-        <v>530.75</v>
+        <v>1197.35</v>
       </c>
       <c r="C122" s="14">
-        <v>431.75</v>
+        <v>771.16</v>
       </c>
       <c r="D122" s="14">
-        <v>156.74</v>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fading</t>
+        <v>847.43</v>
+      </c>
+      <c r="E122" s="14">
+        <v>987.3</v>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero (holding)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="0"/>
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green Fold Over Asymmetric Hem Midi Skirt (MAMC)</t>
+        </is>
+      </c>
+      <c r="B123" s="14">
+        <v>326.4</v>
+      </c>
+      <c r="C123" s="14">
+        <v>397.63</v>
+      </c>
+      <c r="D123" s="14">
+        <v>607.41</v>
+      </c>
+      <c r="E123" s="14">
+        <v>291.22</v>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Email campaigns (Klaviyo)</t>
-        </is>
-      </c>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
-      <c r="J124" s="13"/>
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retro Camisole Layer Top (2th Desire)</t>
+        </is>
+      </c>
+      <c r="B124" s="14">
+        <v>693.66</v>
+      </c>
+      <c r="C124" s="14">
+        <v>547.9</v>
+      </c>
+      <c r="D124" s="14">
+        <v>397.29</v>
+      </c>
+      <c r="E124" s="14">
+        <v>366.3</v>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2TH lone holdout</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Send Date</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Campaign</t>
-        </is>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Theme</t>
-        </is>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recipients</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open Rate</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attributed Rev</t>
-        </is>
-      </c>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conv</t>
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y2K Beaded Multi Strap Top (1Jinn)</t>
+        </is>
+      </c>
+      <c r="B125" s="14">
+        <v>331.17</v>
+      </c>
+      <c r="C125" s="14">
+        <v>594.51</v>
+      </c>
+      <c r="D125" s="14">
+        <v>460.85</v>
+      </c>
+      <c r="E125" s="14">
+        <v>498.76</v>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jun 03</t>
-        </is>
-      </c>
-      <c r="B126" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603 Outthe Blue</t>
-        </is>
-      </c>
-      <c r="C126" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outtheblue</t>
-        </is>
+          <t xml:space="preserve">Polka Dot Stripe Henley Tank 3pc Set (1Jinn)</t>
+        </is>
+      </c>
+      <c r="B126" s="14">
+        <v>464.84</v>
+      </c>
+      <c r="C126" s="14">
+        <v>339.01</v>
       </c>
       <c r="D126" s="14">
-        <v>428</v>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.0%</t>
-        </is>
-      </c>
-      <c r="F126" s="14">
-        <v>56.91</v>
-      </c>
-      <c r="G126" s="14">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E126" s="14">
+        <v>511.33</v>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rebounded</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jun 10</t>
-        </is>
-      </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0610 Outthe Blue vol.2</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outtheblue</t>
-        </is>
+          <t xml:space="preserve">Outtheblue line (vendor total)</t>
+        </is>
+      </c>
+      <c r="B127" s="14">
+        <v>79</v>
+      </c>
+      <c r="C127" s="14">
+        <v>989.58</v>
       </c>
       <c r="D127" s="14">
-        <v>536</v>
-      </c>
-      <c r="E127" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62.1%</t>
-        </is>
-      </c>
-      <c r="F127" s="14">
-        <v>258.22</v>
-      </c>
-      <c r="G127" s="14">
-        <v>1</v>
+        <v>109.97</v>
+      </c>
+      <c r="E127" s="14">
+        <v>712.64</v>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovered (+2.9pp)</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Midnight Meow Zip Up Cat Ear Hoodie (1Jinn)</t>
+        </is>
+      </c>
+      <c r="B128" s="14">
+        <v>530.75</v>
+      </c>
+      <c r="C128" s="14">
+        <v>431.75</v>
+      </c>
+      <c r="D128" s="14">
+        <v>156.74</v>
+      </c>
+      <c r="E128" s="14">
+        <v>225.5</v>
+      </c>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fading</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email campaigns (Klaviyo)</t>
+        </is>
+      </c>
+      <c r="B130" s="13"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="13"/>
+      <c r="J130" s="13"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Send Date</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campaign</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theme</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recipients</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open Rate</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attributed Rev</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 03</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0603 Outthe Blue</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outtheblue</t>
+        </is>
+      </c>
+      <c r="D132" s="14">
+        <v>428</v>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66.0%</t>
+        </is>
+      </c>
+      <c r="F132" s="14">
+        <v>56.91</v>
+      </c>
+      <c r="G132" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 10</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0610 Outthe Blue vol.2</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outtheblue</t>
+        </is>
+      </c>
+      <c r="D133" s="14">
+        <v>536</v>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62.1%</t>
+        </is>
+      </c>
+      <c r="F133" s="14">
+        <v>258.22</v>
+      </c>
+      <c r="G133" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jun 13</t>
         </is>
       </c>
-      <c r="B128" s="14" t="inlineStr">
+      <c r="B134" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0613 MAMC</t>
         </is>
       </c>
-      <c r="C128" s="14" t="inlineStr">
+      <c r="C134" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">MAMC</t>
         </is>
       </c>
-      <c r="D128" s="14">
+      <c r="D134" s="14">
         <v>536</v>
       </c>
-      <c r="E128" s="14" t="inlineStr">
+      <c r="E134" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">59.6%</t>
         </is>
       </c>
-      <c r="F128" s="14">
+      <c r="F134" s="14">
         <v>316.7</v>
       </c>
-      <c r="G128" s="14">
+      <c r="G134" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="14" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 17</t>
         </is>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B135" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">0617 2th Desire</t>
         </is>
       </c>
-      <c r="C129" s="14" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">2th Desire</t>
         </is>
       </c>
-      <c r="D129" s="14">
+      <c r="D135" s="14">
         <v>552</v>
       </c>
-      <c r="E129" s="14" t="inlineStr">
+      <c r="E135" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">61.5%</t>
         </is>
       </c>
-      <c r="F129" s="14">
+      <c r="F135" s="14">
         <v>75</v>
       </c>
-      <c r="G129" s="14">
+      <c r="G135" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 23</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0623 Delete-Ex</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete-Ex</t>
+        </is>
+      </c>
+      <c r="D136" s="14">
+        <v>626</v>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60.2%</t>
+        </is>
+      </c>
+      <c r="F136" s="14">
+        <v>133</v>
+      </c>
+      <c r="G136" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">YEAR-OVER-YEAR (2026 vs 2025)</t>
         </is>
       </c>
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="15"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
+      <c r="B138" s="15"/>
+      <c r="C138" s="15"/>
+      <c r="D138" s="15"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="15"/>
+      <c r="G138" s="15"/>
+      <c r="H138" s="15"/>
+      <c r="I138" s="15"/>
+      <c r="J138" s="15"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="0"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">GMV vs same week last year</t>
         </is>
       </c>
-      <c r="B133" s="16"/>
-      <c r="C133" s="16"/>
-      <c r="D133" s="16"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="16"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="16"/>
-      <c r="I133" s="16"/>
-      <c r="J133" s="16"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
+      <c r="B140" s="16"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="16"/>
+      <c r="I140" s="16"/>
+      <c r="J140" s="16"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 Week</t>
         </is>
       </c>
-      <c r="B134" s="15" t="inlineStr">
+      <c r="B141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 GMV</t>
         </is>
       </c>
-      <c r="C134" s="15" t="inlineStr">
+      <c r="C141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2025 Matched Week</t>
         </is>
       </c>
-      <c r="D134" s="15" t="inlineStr">
+      <c r="D141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2025 GMV</t>
         </is>
       </c>
-      <c r="E134" s="15" t="inlineStr">
+      <c r="E141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2025 Orders</t>
         </is>
       </c>
-      <c r="F134" s="15" t="inlineStr">
+      <c r="F141" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">YoY</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="17" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">May 11–17</t>
         </is>
       </c>
-      <c r="B135" s="17">
+      <c r="B142" s="17">
         <v>12555.04</v>
       </c>
-      <c r="C135" s="17" t="inlineStr">
+      <c r="C142" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of May 12 2025</t>
         </is>
       </c>
-      <c r="D135" s="17">
+      <c r="D142" s="17">
         <v>3909.81</v>
       </c>
-      <c r="E135" s="17">
+      <c r="E142" s="17">
         <v>23</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+221%</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="17" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">May 18–24</t>
         </is>
       </c>
-      <c r="B136" s="17">
+      <c r="B143" s="17">
         <v>16016.78</v>
       </c>
-      <c r="C136" s="17" t="inlineStr">
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of May 19 2025</t>
         </is>
       </c>
-      <c r="D136" s="17">
+      <c r="D143" s="17">
         <v>3478.49</v>
       </c>
-      <c r="E136" s="17">
+      <c r="E143" s="17">
         <v>25</v>
       </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+360%</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="17" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">May 25–31</t>
         </is>
       </c>
-      <c r="B137" s="17">
+      <c r="B144" s="17">
         <v>13905.39</v>
       </c>
-      <c r="C137" s="17" t="inlineStr">
+      <c r="C144" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of May 26 2025</t>
         </is>
       </c>
-      <c r="D137" s="17">
+      <c r="D144" s="17">
         <v>7821.55</v>
       </c>
-      <c r="E137" s="17">
+      <c r="E144" s="17">
         <v>47</v>
       </c>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">+78%</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="17" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 1–7</t>
         </is>
       </c>
-      <c r="B138" s="17">
+      <c r="B145" s="17">
         <v>17663.96</v>
       </c>
-      <c r="C138" s="17" t="inlineStr">
+      <c r="C145" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of Jun 02 2025</t>
         </is>
       </c>
-      <c r="D138" s="17">
+      <c r="D145" s="17">
         <v>18559.83</v>
       </c>
-      <c r="E138" s="17">
+      <c r="E145" s="17">
         <v>195</v>
       </c>
-      <c r="F138" s="4" t="inlineStr">
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-4.8%</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="17" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 8–14</t>
         </is>
       </c>
-      <c r="B139" s="17">
+      <c r="B146" s="17">
         <v>15074.88</v>
       </c>
-      <c r="C139" s="17" t="inlineStr">
+      <c r="C146" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of Jun 09 2025</t>
         </is>
       </c>
-      <c r="D139" s="17">
+      <c r="D146" s="17">
         <v>18199.18</v>
       </c>
-      <c r="E139" s="17">
+      <c r="E146" s="17">
         <v>171</v>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-17.2%</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="17" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Jun 15–21</t>
         </is>
       </c>
-      <c r="B140" s="17">
+      <c r="B147" s="17">
         <v>13916.5</v>
       </c>
-      <c r="C140" s="17" t="inlineStr">
+      <c r="C147" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">wk of Jun 16 2025</t>
         </is>
       </c>
-      <c r="D140" s="17">
+      <c r="D147" s="17">
         <v>22144.84</v>
       </c>
-      <c r="E140" s="17">
+      <c r="E147" s="17">
         <v>214</v>
       </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">-37.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jun 22–28</t>
+        </is>
+      </c>
+      <c r="B148" s="17">
+        <v>19353.59</v>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wk of Jun 23 2025</t>
+        </is>
+      </c>
+      <c r="D148" s="17">
+        <v>22070.41</v>
+      </c>
+      <c r="E148" s="17">
+        <v>195</v>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-12.3%</t>
         </is>
       </c>
     </row>
